--- a/data/outputs/4. Moorgate Crossrail Register (Final).xlsx
+++ b/data/outputs/4. Moorgate Crossrail Register (Final).xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Delayed opening of Moorgate Crossrail station.</t>
+          <t>Opening of the Moorgate Crossrail station is delayed further.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Stakeholder</t>
+          <t>Adjoining Owners</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -539,12 +539,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Regular engagement with Crossrail to allow for alternative arrangements.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>Regular engagement with Crossrail from now to 2020/2021 to allow for alternative arrangements should there be a delay in delivery.</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -559,7 +567,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Riney highways contract expiration may require a new Principal Contractor if construction is delayed.</t>
+          <t>Slippage in construction start may require finding a new Principal Contractor after the Riney highways contract expires in summer 2022.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -590,12 +598,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Discussions to take place internally should this risk look more probable on how work would be transferred to a new contractor- or not</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>Initiate internal discussions on contingency plans for transferring work to a new contractor if needed.</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -610,7 +626,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Delays in surrounding developments risk final project delivery phases.</t>
+          <t>Delays to the four developments surrounding the Moorgate Crossrail station delay the final delivery phases of the MCSL project.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -620,7 +636,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stakeholder</t>
+          <t>Adjoining Owners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -641,12 +657,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Regular engagement with developers to allow for alternative arrangements and early notification of delays.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>Regular engagement with developers from now until the completion of the developments to allow for alternative arrangements and early notification of delays.</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -661,12 +685,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Infrastructure and utilities difficulties at Moorgate junction may hinder design, transformation, and safety enhancements.</t>
+          <t>Infrastructure and utilities difficulties at the Moorgate junction make it difficult and expensive to design and transform the space while enhancing safety.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -676,11 +700,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Lead engineer</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -692,12 +716,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Set expectations early and work with stakeholders to identify alternative design solutions.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>Monitor and evaluate.</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -712,7 +744,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Key stakeholders may not endorse design options.</t>
+          <t>Key stakeholder(s) do not endorse design options.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -743,12 +775,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Ensure Stakeholder Working Group is suitably engaged and design options are presented with clear rationale.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>Ensure that the Stakeholder Working Group is suitably engaged and informed to secure endorsement.</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -763,7 +803,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Delays or changes to dependency projects like Beech Street and St. Paul's Gyratory.</t>
+          <t>Delays or changes to dependency projects like Beech Street and St. Paul's Gyratory could impact project timelines.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -773,7 +813,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Adjoining Owners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -794,12 +834,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Work with internal stakeholders to minimize any impacts should changes arise</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+          <t>Work with internal stakeholders to minimize any impacts should changes arise.</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -814,12 +862,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Breakdown in engagement with key stakeholders.</t>
+          <t>Breakdown in engagement with key stakeholders, such as Islington Council.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Multiple (Or All) Life Phases</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -845,12 +893,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ensure coherent communications at strategic points, particularly on boundary solutions.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>Ensure coherent communications with stakeholders at strategic points throughout the project, particularly regarding proposed boundary solutions.</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -865,7 +921,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TfL restructure may lead to insufficient dedicated resources for required approvals.</t>
+          <t>TfL restructure may result in no dedicated scheme sponsor or resource being allocated to progress required TfL approvals.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -875,7 +931,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stakeholder</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -884,24 +940,32 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Med</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Seek early resource establishment and maintain close contact for reassurances.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>Officers will seek to establish resources early and maintain close contact to understand the restructure's extent, seeking resource reassurance if needed.</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -916,7 +980,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The proposed scheme may negatively impact protected characteristics under the Equalities Act.</t>
+          <t>The proposed scheme could negatively impact protected characteristics under the Equalities Act 2010.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -926,33 +990,41 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stakeholder</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Meetings with representative groups and EA Team for design feedback; prepare EA plan.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>Conduct regular meetings with representative groups and engage the EA Team for design feedback to prepare an EA plan.</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -967,12 +1039,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Traffic resilience requirements restrict design options.</t>
+          <t>Traffic resilience requirements restrict design options for Moorgate junctions.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -982,7 +1054,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Lead engineer</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -998,12 +1070,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Ensure appropriate resilience in Moorgate junction designs at London Wall and Ropemaker Street.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+          <t>Ensure appropriate resilience levels are incorporated into Moorgate junction designs at London Wall and Ropemaker Street.</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/outputs/4. Moorgate Crossrail Register (Final).xlsx
+++ b/data/outputs/4. Moorgate Crossrail Register (Final).xlsx
@@ -431,99 +431,99 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Risk ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Project Stage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Project Category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Owner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mitigating Action</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Likelihood (1-10) (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Impact (1-10) (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Priority (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Likelihood (1-10) (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Impact (1-10) (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Priority (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Date Added</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Risk ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Project Stage</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Project Category</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Owner</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (1-10) (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (1-10) (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Priority (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Mitigating Action</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (1-10) (post-mitigation)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (1-10) (post-mitigation)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Priority (post-mitigation)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Opening of the Moorgate Cross rail station is delayed further.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Opening of the Moorgate Crossrail station is delayed further.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adjoining Owners</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Regular engagement with Crossrail from now to 2020/2021. This should allow for alternative arrangements to be made should there be a delay in the delivery of Crossrail.</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -537,111 +537,111 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Regular engagement with Crossrail from now to 2020/2021 to allow for alternative arrangements should there be a delay in delivery.</t>
-        </is>
+      <c r="J2" t="n">
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" t="n">
         <v>2</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>The Riney highways contract is due to expire in the summer of 2022. Any slippage in starting the construction programme may mean we have to consider a new Principal Contractor for the later stages of delivery.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Slippage in construction start may require finding a new Principal Contractor after the Riney highways contract expires in summer 2022.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Procurement Manager</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Discussions to take place internally should this risk look more probable on how work would be transferred to a new contractor- or not</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Initiate internal discussions on contingency plans for transferring work to a new contractor if needed.</t>
-        </is>
+      <c r="J3" t="n">
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>2</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Delays to the four developments surrounding the Moorgate Crossrail station delay the final delivery phases of the MCSL project</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Delays to the four developments surrounding the Moorgate Crossrail station delay the final delivery phases of the MCSL project.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Adjoining Owners</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Adjoining Owners</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Regular engagement with developers from now until the completion of the developments. This should allow for alternative arrangements to be made should there be a delay in the delivery of the developments and mean that we find out as early as possible about any delays.</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -655,96 +655,96 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Regular engagement with developers from now until the completion of the developments to allow for alternative arrangements and early notification of delays.</t>
-        </is>
+      <c r="J4" t="n">
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>Infrastructure and utilities difficulties at the Moorgate junction with London Wall and with Ropermaker Street, make it difficult/too expensive to design and transform the space, as well as enhance safety.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Infrastructure and utilities difficulties at the Moorgate junction make it difficult and expensive to design and transform the space while enhancing safety.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Infrastructure Manager</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Set expectations at the earliest stage possible where it is discovered that there are major physical constraints. Work closely with internal and external stakeholders to identify design solutions to bring the work forward that might not require such extensive physical changes.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Monitor and evaluate.</t>
-        </is>
+      <c r="J5" t="n">
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>Key stakeholder(s) do not endorse design options</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Key stakeholder(s) do not endorse design options.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stakeholder</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Ensure that Stakeholder Working Group is suitably</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -773,52 +773,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Ensure that the Stakeholder Working Group is suitably engaged and informed to secure endorsement.</t>
-        </is>
+      <c r="J6" t="n">
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>Delays/changes to dependency projects, such as Beech Street and St. Paul's Gyratory.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Delays or changes to dependency projects like Beech Street and St. Paul's Gyratory could impact project timelines.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Adjoining Owners</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Work with internal stakeholders to minimize any impacts should changes arise</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -832,52 +832,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Work with internal stakeholders to minimize any impacts should changes arise.</t>
-        </is>
+      <c r="J7" t="n">
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>Breakdown in engagement with key stakeholders, such as Islington Council.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Breakdown in engagement with key stakeholders, such as Islington Council.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Multiple (Or All) Life Phases</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stakeholder</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Ensure coherent communications with stakeholders and ensure stakeholders are communicated with at strategic points throughout the project. Particularly proposed boundary solutions</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -891,111 +891,111 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Ensure coherent communications with stakeholders at strategic points throughout the project, particularly regarding proposed boundary solutions.</t>
-        </is>
+      <c r="J8" t="n">
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>TfL restructure may mean that no dedicated scheme sponsor / resource can be allocated to progress any required TfL approvals.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TfL restructure may result in no dedicated scheme sponsor or resource being allocated to progress required TfL approvals.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Officers will seek to establish resources as early as possible and keep close contact to understand the extent of the restructure, seeking reassurance of resource if needed.</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Officers will seek to establish resources early and maintain close contact to understand the restructure's extent, seeking resource reassurance if needed.</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6</v>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>There is a potential that the proposed scheme could impact negatively on the protected characteristics under the Equalities Act, 2010.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The proposed scheme could negatively impact protected characteristics under the Equalities Act 2010.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Meetings with representative groups will be conducted regularly to design out issues of concern. The EA Team will be engaged regularly for design feedback. An EA plan will be prepared as part of the project.</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1009,37 +1009,37 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Conduct regular meetings with representative groups and engage the EA Team for design feedback to prepare an EA plan.</t>
-        </is>
+      <c r="J10" t="n">
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>Requirement to keep the ability for resilience/flexibility through the area in traffic terms, restricts the options that can be developed.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Traffic resilience requirements restrict design options for Moorgate junctions.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design Manager</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Seek to ensure that an appropriate level of resilience is allowed for when designing Moorgate junctions at London Wall and Ropemaker Street.</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1068,20 +1068,20 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Ensure appropriate resilience levels are incorporated into Moorgate junction designs at London Wall and Ropemaker Street.</t>
-        </is>
+      <c r="J11" t="n">
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
